--- a/sports_forms/002_sports_league_data_collection_consent_form--sports_forms.xlsx
+++ b/sports_forms/002_sports_league_data_collection_consent_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'parent/guardian'}</t>
+          <t>parent/guardian</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Parent/Guardian'}</t>
+          <t>Parent/Guardian</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'coach/manager'}</t>
+          <t>coach/manager</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Coach/Manager'}</t>
+          <t>Coach/Manager</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'parent/guardian'}</t>
+          <t>parent/guardian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Parent/Guardian'}</t>
+          <t>Parent/Guardian</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'coach/manager'}</t>
+          <t>coach/manager</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Coach/Manager'}</t>
+          <t>Coach/Manager</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'i_consent_to_the_collection_and_processing_of_my_participant_information.'}</t>
+          <t>i_consent_to_the_collection_and_processing_of_my_participant_information.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'I consent to the collection and processing of my participant information.'}</t>
+          <t>I consent to the collection and processing of my participant information.</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_consent_to_the_collection_and_processing_of_my_participant_information.'}</t>
+          <t>i_do_not_consent_to_the_collection_and_processing_of_my_participant_information.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'I do not consent to the collection and processing of my participant information.'}</t>
+          <t>I do not consent to the collection and processing of my participant information.</t>
         </is>
       </c>
     </row>
